--- a/exemple-souhaits.xlsx
+++ b/exemple-souhaits.xlsx
@@ -160,19 +160,19 @@
     <t>Principale</t>
   </si>
   <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>08/05/2026</t>
-  </si>
-  <si>
-    <t>04/05/2026</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>S2</t>
